--- a/ig/DM-OCTOBRE-2024/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2024/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -354,7 +354,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>Equipement adapté à l'obésité massive (&lt; 180 kg)</t>
+    <t>Equipement de rééducation adapté à l'obésité</t>
   </si>
   <si>
     <t>110</t>
